--- a/Automatizacion Envio Masivo de Correos/cola_envios.xlsx
+++ b/Automatizacion Envio Masivo de Correos/cola_envios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,16 @@
           <t>info@gestoriabelen.com</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:54</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -526,6 +536,16 @@
           <t>jm@gesser.info</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:54</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -563,6 +583,16 @@
           <t>meitel@mtassessors.com</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:54</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -600,6 +630,16 @@
           <t>info@ogima.es</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:54</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -637,6 +677,16 @@
           <t>info@gestaliagrup.com</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:54</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -674,6 +724,16 @@
           <t>info@tributaliabogados.com</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:54</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -711,6 +771,16 @@
           <t>info@mezquidaconsultors.com</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:55</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -748,6 +818,16 @@
           <t>asein@aseintarragona.com</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:55</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -785,6 +865,16 @@
           <t>gestorboronat@gestores.net</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:55</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -822,6 +912,16 @@
           <t>tarragona@azvconsulting.com</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:55</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -859,6 +959,16 @@
           <t>assandra@tiservinet.es</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:55</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -896,6 +1006,16 @@
           <t>gesriola@gestores.net</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:55</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -933,6 +1053,16 @@
           <t>info@gadin.cat</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:55</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -970,6 +1100,16 @@
           <t>buch@assessoriabuch.com</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:56</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1007,6 +1147,16 @@
           <t>maresmeabogados@gmail.com</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:56</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1044,6 +1194,16 @@
           <t>gestomart@gestores.net</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:56</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1081,6 +1241,16 @@
           <t>info@gestoriabarcelo.com</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:56</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1118,6 +1288,16 @@
           <t>info@gestoriamaresme.com</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:56</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1155,6 +1335,16 @@
           <t>gestoriallado@gestorialladomataro.es</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:56</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1192,6 +1382,16 @@
           <t>administracion@asesoriagoti.com</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:56</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1229,6 +1429,16 @@
           <t>info@easygest.es</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1266,6 +1476,16 @@
           <t>info@maringles.com</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1303,6 +1523,16 @@
           <t>info@bleconomistes.com</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1340,6 +1570,16 @@
           <t>roser@ametller-economistes.com</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1377,6 +1617,16 @@
           <t>administracion@asesoria-iluro.com</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1414,6 +1664,16 @@
           <t>info@rodonverges.com</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1451,6 +1711,16 @@
           <t>info@assessoriagaro.com</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1488,6 +1758,16 @@
           <t>cecassa@cecassa.com</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:57</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1525,6 +1805,16 @@
           <t>xifra@assessoriaxifra.com</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:58</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1562,6 +1852,16 @@
           <t>gestoria@vilanovagestio.com</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:58</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1599,6 +1899,16 @@
           <t>info@gestalassessors.com</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:58</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1636,6 +1946,16 @@
           <t>vidal@vidalpiqueassessors.cat</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:58</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1673,6 +1993,16 @@
           <t>ggf@grupgestiofiscal.com</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:58</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1710,6 +2040,16 @@
           <t>info@premiavng.com</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:58</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1747,6 +2087,16 @@
           <t>hernandez@gestors.net</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:58</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1784,6 +2134,16 @@
           <t>9@9assessors.com</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1821,6 +2181,16 @@
           <t>ceteb@ceteb.com</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1858,6 +2228,16 @@
           <t>info@gespasgestoria.com</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1895,6 +2275,16 @@
           <t>info@martinezassessors.com</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1932,6 +2322,16 @@
           <t>solfico@solfico.es</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1969,6 +2369,16 @@
           <t>info@invalgestoria.com</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2006,6 +2416,16 @@
           <t>gestiona@gestionasolucions.cat</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2043,6 +2463,16 @@
           <t>grup4@grupquatre.es</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2080,6 +2510,16 @@
           <t>ayases@ayases.es</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:59</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2117,6 +2557,16 @@
           <t>info@grupintegraconsulting.com</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:00</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2154,6 +2604,16 @@
           <t>acantos@ardebolassessors.cat</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:00</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2191,6 +2651,16 @@
           <t>info@gestoriamartorell.com</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:00</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2228,6 +2698,16 @@
           <t>info@gestoriacerdanyola.com</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:00</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2265,6 +2745,16 @@
           <t>info@grupsisquella.com</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:00</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2302,6 +2792,16 @@
           <t>info@gaag.es</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:00</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2339,6 +2839,16 @@
           <t>grupdos@grupdos.com</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:00</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2376,6 +2886,16 @@
           <t>info@gestoriasbarcelona.com</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:00</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2413,6 +2933,11 @@
           <t>administracion@a-csn.com</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2450,6 +2975,11 @@
           <t>info@assessoriacerdanyola.com</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2487,6 +3017,11 @@
           <t>albadalejo@gestors.net</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2524,6 +3059,11 @@
           <t>simon@serveissimon.com</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2561,6 +3101,11 @@
           <t>info@gapassessors.com</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2598,6 +3143,11 @@
           <t>scc@santcugatconsulting.com</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2635,6 +3185,11 @@
           <t>administracio@tramitserveis.cat</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2672,6 +3227,11 @@
           <t>gacgrup@gacgrup.com</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2709,6 +3269,11 @@
           <t>edit@editconsultores.com</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2746,6 +3311,11 @@
           <t>info@plusgestio.com</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2783,6 +3353,11 @@
           <t>asenta@asenta.es</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2820,6 +3395,11 @@
           <t>info@indeedasesores.com</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2857,6 +3437,11 @@
           <t>info@gestoriajuncosas.com</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2894,6 +3479,11 @@
           <t>pablo@adesantcugat.es</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2931,6 +3521,11 @@
           <t>josep@gestoriacapmany.com</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2968,6 +3563,11 @@
           <t>rubigest@rubigest.com</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3005,6 +3605,16 @@
           <t>gestoriajulia@gmail.com</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>enviado</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:03</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3042,6 +3652,11 @@
           <t>info@rubiasesores.com</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3079,6 +3694,11 @@
           <t>antonio@consultoriamorenomartinez.com</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3116,6 +3736,11 @@
           <t>info@asesoresgs.com</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3153,6 +3778,11 @@
           <t>rovira@gabinet-rovira.com</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3190,6 +3820,11 @@
           <t>cet4@cet4.es</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3227,6 +3862,11 @@
           <t>hola@busbac.com</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3264,6 +3904,11 @@
           <t>ridao@gesridao.com</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3301,6 +3946,11 @@
           <t>info@gestoriavilafranca.com</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3338,6 +3988,11 @@
           <t>info@cypassessors.cat</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3375,6 +4030,11 @@
           <t>info@decaraassessors.com</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3412,6 +4072,11 @@
           <t>info@gestoriaplanas.com</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3449,6 +4114,11 @@
           <t>info@gestoriaolivella.com</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3486,6 +4156,11 @@
           <t>acobo@gestoriasole.com</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3523,6 +4198,11 @@
           <t>admin@consultingpenedes.cat</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3560,6 +4240,11 @@
           <t>freixedas@gestors.net</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3597,6 +4282,11 @@
           <t>hola@serestal.cat</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3634,6 +4324,11 @@
           <t>csdbaimpost@msn.com</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3671,6 +4366,11 @@
           <t>gestoria@osorioconsulting.net</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3708,6 +4408,11 @@
           <t>info@solucionsempresarialspenedes.com</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3745,6 +4450,11 @@
           <t>hola@1mes1gestio.com</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>error: (451, b'4.7.1 Ratelimit "hostinger_out_ratelimit" exceeded for key "RLbxrhexzdqcgeg1nuh5wcackb"')</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -4006,7 +4716,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4043,7 +4753,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4080,7 +4790,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4117,7 +4827,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4154,7 +4864,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4191,7 +4901,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4228,7 +4938,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4265,7 +4975,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4302,7 +5012,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -4339,7 +5049,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -4567,6 +5277,4545 @@
       <c r="I112" t="inlineStr">
         <is>
           <t>https://www.gestorias.es/girona/figueres/delta-grup-assessors-15363</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>equip de Asesoría del Vallès</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Asesoría del Vallès</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>info@asesoriavalles.es</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>http://asesoriavalles.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>equip de Lex Valles Associats</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Lex Valles Associats</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>info@lexvalles.com</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://lexvalles.es/contacto-asesoria-en-mollet/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>equip de Fortuny i Janoher</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Fortuny i Janoher</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>info@fortuny-janoher.com</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>http://www.fortuny-janoher.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>equip de AISM S.L.</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>AISM S.L.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>aism@asesoria-aism.com</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>https://aismasesoria.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>equip de Gabinet Emiliano i Associats, S.L.</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Gabinet Emiliano i Associats, S.L.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>info@gabinetemiliano.com</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>https://www.gabineteemiliano.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>equip de Asesoría Gala (Gala S.C.P.)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Asesoría Gala (Gala S.C.P.)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>gala@asesoriagala.com</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>https://asesoriagala.com/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>equip de Dynamic Advisers</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Dynamic Advisers</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>info@dynamicadvisers.com</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>https://www.dynamicadvisers.com/gestoria-mollet-del-valles-dynamic-advisers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>equip de Gestoria Romo</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Gestoria Romo</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>gestoria@gestoriaromo.com</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>http://www.gestoriaromo.com/contactar-con-gestoria-romo-en-cornella-de-llobregat</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>equip de Seci Asesores</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Seci Asesores</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>seciasesores@seci.biz</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>https://www.seciasesores.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>equip de Gestoría GesRosas</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Gestoría GesRosas</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>info@gesrosas.es</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>https://www.cylex.es/cornella-de-llobregat/gestor%C3%ADa-gesrosas-13269099.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>equip de Baix Asesoramiento y Gestión S.L.</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Baix Asesoramiento y Gestión S.L.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>consultas@asesoriabaix.com</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>https://www.asesoriabaix.es/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>equip de Gestoría Palacios</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Gestoría Palacios</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>info@gpalacios.com</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>https://gestoriapalacios.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>equip de SEVIC Asesoría</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SEVIC Asesoría</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>info@asesoriasevic.com</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>https://asesoriasevic.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>equip de Esconfi</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Esconfi</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>esconfi@esconfi.es</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>https://esconfi.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>equip de Assebaix</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Assebaix</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>anna@assebaix.com</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>https://www.assebaix.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>equip de La Asesoría (Cornellà)</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>La Asesoría (Cornellà)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>laasesoria.documents9@gmail.com</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>https://laasesoriacornella.com/la-asesoria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>equip de Asesoría Taxperts</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Asesoría Taxperts</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>comercial@taxperts.es</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>https://www.taxperts.es/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>equip de Fiscount Tax &amp; Accounting S.L.</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Fiscount Tax &amp; Accounting S.L.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>info@fiscount.es</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>https://fiscount.weebly.com/contacto.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>equip de Assellob</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Assellob</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>info@assellob.net</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://assellob.net/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>equip de TG Assessoria Fiscal</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TG Assessoria Fiscal</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>tgassessoria@tgassessoria.com</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://www.qdq.com/t-g-assesoria-fiscal-scp-826098</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>equip de Anteo Asesoría en Cornellà</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Anteo Asesoría en Cornellà</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>info@anteoetl.com</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://anteo.es/en/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>equip de Agestem S.L.</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Agestem S.L.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>asesoria@agestem.com</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>https://www.agestem.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>equip de Moreno Salcedo Abogados y Economistas</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Moreno Salcedo Abogados y Economistas</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>info@morenosalcedo.com</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>https://morenosalcedo.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>equip de Daspime S.L.</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Daspime S.L.</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>bego@daspime.net</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/cornella-de-llobregat/daspime-s-l_233001569_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>equip de Assessoria i Gestió Negre</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Assessoria i Gestió Negre</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>info@assessorianegre.com</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>https://assessorianegre.com/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>equip de ARSA Gestión</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ARSA Gestión</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>info@arsagestion.com</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>https://www.arsagestion.com/asesoria-sant-boi</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>equip de Assessoria Mendiola</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Assessoria Mendiola</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>amendiola@amendiola.es</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>https://www.amendiola.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>equip de TDR Assessors</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>TDR Assessors</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>info@tdrassessors.com</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>https://tdrassessors.com/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>equip de Assessoria Sant Boi S.L.</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Assessoria Sant Boi S.L.</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>josep@assessoriasantboi.cat</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/sant-boi-de-llobregat/assessoria-sant-boi_021273131_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>equip de Raurich Asesores</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Raurich Asesores</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>info@raurich-asesores.com</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://raurich-asesores.com/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>equip de Balada Assessors</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Balada Assessors</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>olga@balada-assessors.com</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://www.balada-assessors.com/es</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>equip de Gestoria Simon &amp; Torrent</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Gestoria Simon &amp; Torrent</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>info@gestoriasimon.com</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://www.gestoriasimon.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>equip de Fiscprat S.L.</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Fiscprat S.L.</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>fiscal@fiscprat.es</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://fiscprat.es/gestoria-en-el-prat-de-llobregat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>equip de Asesoria Carniago S.L.</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Asesoria Carniago S.L.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>asesoria@carniago.com</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>http://carniago.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>equip de Gabinete/Asesoría Delta</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Gabinete/Asesoría Delta</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>gestion@asesoriadelta.com</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://www.asesoriadelta.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>equip de 2A Assessors</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2A Assessors</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>info@2aassessors.com</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://www.2aassessors.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>equip de Forum Legal y Económico</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Forum Legal y Económico</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>forum@forumlegalyeconomico.com</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>https://www.forumlegalyeconomico.com/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>equip de Grup 3 Assessors</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Grup 3 Assessors</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>info@grup3assessors.com</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://grup3assessors.com/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>equip de Delaw Assessors S.L.</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Delaw Assessors S.L.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>delaw@delaw.es</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://www.guia33.com/item/delaw-assessors-el-prat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>equip de Kosmos Asesores</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Kosmos Asesores</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>info@kosmosasesores.com</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>https://kosmosasesores.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>equip de ACM Asesores</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ACM Asesores</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>acm@acmsl.es</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://www.asesoriaelprat.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>equip de Gestoría BERNI</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Gestoría BERNI</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>berni@grupfabrega.com</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>https://www.gestoriabernifabrega.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>equip de GEMAP</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>GEMAP</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>gemap@gemap.es</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>https://gemap.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>equip de Ariza Gestoría</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Ariza Gestoría</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>m-ariza@telefonica.net</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>https://www.gestoria-ariza.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>equip de Vistamar Gestión Empresarial</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Vistamar Gestión Empresarial</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>info@vistamar.cat</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>http://vistamar.cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>equip de Ingesdat 2008 S.L.</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Ingesdat 2008 S.L.</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>ingesdat@hotmail.es</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>https://empresite.eleconomista.es/INGESDAT-2008.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>equip de Quatro Gestión</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Quatro Gestión</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>resteban@consultoriakoymark.com</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>https://quatrogestion.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>equip de Centre de Gestions Molins</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Centre de Gestions Molins</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>aleix@centredegestions.com</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>https://centredegestions.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>equip de Molins Legal</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Molins Legal</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>info@molinslegal.com</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>https://molinslegal.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>equip de Sabaté i Matas Associats (Centre de Càlcul)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Sabaté i Matas Associats (Centre de Càlcul)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>esteve@centredecalcul.net</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>http://www.centredecalcul.net/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>equip de E-D'ASS</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>E-D'ASS</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>e-dass@e-dass.com</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>https://e-dass.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>equip de Gestoría VP</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Gestoría VP</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>info@gestoriavp.com</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>https://gestoriavp.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>equip de Gimeno Assessoria Jurídica (Gestoria Gimeno)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Gimeno Assessoria Jurídica (Gestoria Gimeno)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>comptabilitats@gimeno.net</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>https://www.gimeno.net/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>equip de Asesoría Integral Gesticat Plus</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Asesoría Integral Gesticat Plus</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>info@gesticat.com</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>https://gesticat.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>equip de Alzueta &amp; Saperas Assessors</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Alzueta &amp; Saperas Assessors</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>recepcion@alzuetaysaperas.com</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>https://alzuetaysaperas.com/contacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>equip de Gestions Empresarials Cabirol S.L.</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Gestions Empresarials Cabirol S.L.</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>info@cabirol.cat</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>https://cabirolsl.com/contacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>equip de Tax Molins de Rei (Agesa)</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Tax Molins de Rei (Agesa)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>asfilsa@agesa.es</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>https://www.tax.es/es/oficinas/cataluna/tax-molins-de-rei.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>equip de Gestoría Viaplana (Viaplana Multigestió)</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Gestoría Viaplana (Viaplana Multigestió)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/mollet-del-valles/gestoria-viaplana-470</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>equip de Assessoria i Serveis Empresarials Costa</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Assessoria i Serveis Empresarials Costa</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/a/asesores-y-asesorias/barcelona/mollet-del-valles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>equip de AR Asesores Mollet</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>AR Asesores Mollet</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>https://www.gestoriavalles.es/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>equip de GCA Asesoría</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>GCA Asesoría</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/mollet-del-valles/gca_001804467_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>equip de Gypesa</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Gypesa</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/mollet-del-valles/gypesa-9131</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>equip de Gestoría Vallès</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Gestoría Vallès</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/mollet-del-valles/gestoria-valles-17920</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>equip de Valles Gestió</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Valles Gestió</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/mollet-del-valles/valles-gestio-16561</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>equip de Poch Assessors</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Poch Assessors</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/mollet-del-valles/poch-assessors_020831442_000000003.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>equip de Mayolas Assessors d'Empreses</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Mayolas Assessors d'Empreses</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/a/asesores-y-asesorias/barcelona/mollet-del-valles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>equip de Diperex S.L.</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Diperex S.L.</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>https://www.einforma.com/informacion-empresa/diperex-slp</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>equip de Bemtronic Online S.L.</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Bemtronic Online S.L.</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/a/asesores-y-asesorias/barcelona/mollet-del-valles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>equip de Assessoria Joan Mercadal S.L.</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Assessoria Joan Mercadal S.L.</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>https://www.citiservi.es/barcelona/assessoria-joan-mercadal-mollet-del-valles__930002_67.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>equip de Salvador Lopez Molina</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Salvador Lopez Molina</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/a/asesores-y-asesorias/barcelona/mollet-del-valles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>equip de Rosa Bravo López</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Rosa Bravo López</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/a/asesorias-laborales/barcelona/mollet-del-valles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>equip de Ecofinancial Group Consulting 86 S.L.</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Ecofinancial Group Consulting 86 S.L.</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mollet del Vallès</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/a/asesores-y-asesorias/barcelona/mollet-del-valles/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>equip de J.M. Medina S.L.</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>J.M. Medina S.L.</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/cornella-de-llobregat/j-m-medina-1673</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>equip de Asesoría Roser Camps S.L.</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Asesoría Roser Camps S.L.</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/cornella-de-llobregat/asesoria-roser-camps-s-l-_014410344_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>equip de Gestión y Asesoramientos Cornellà</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Gestión y Asesoramientos Cornellà</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/cornella-de-llobregat/gestion-y-asesoramientos-cornella-9711</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>equip de D.M. Asesoría</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>D.M. Asesoría</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>https://firmania.es/cornella-de-llobregat/dm-asesor%C3%ADa-1693298</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>equip de Berule Consult S.L.</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Berule Consult S.L.</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Cornellà de Llobregat</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>https://firmania.es/cornella-de-llobregat/berule-consult-sl-1797127</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>equip de Gestoria Abella Gestió</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Gestoria Abella Gestió</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/sant-boi-de-llobregat/gestoria-abella-gestio_000581736_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>equip de Gabinet Assessor Ros</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Gabinet Assessor Ros</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/sant-boi-de-llobregat/gabinet-assessor-ros_172254500_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>equip de Bufet Assessor ADEC S.L.P.</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Bufet Assessor ADEC S.L.P.</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>https://infonif.economia3.com/ficha-empresa/bufet-assessor-adec-slp</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>equip de Assessoria Integral de Sant Boi S.L.</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Assessoria Integral de Sant Boi S.L.</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>https://empresite.eleconomista.es/ASSESSORIA-INTEGRAL-SANT-BOI.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>equip de Vikmer Assessors S.L.P.</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Vikmer Assessors S.L.P.</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/sant-boi-de-llobregat/vikmer-assessors-19018</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>equip de Bgr Assessors</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Bgr Assessors</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/sant-boi-de-llobregat/bgr-assessors_159456037_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>equip de Gramalla XXI Assessors al seu Servei</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Gramalla XXI Assessors al seu Servei</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>https://www.gramallaxxi.es/?lang=es</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>equip de Aba Serveis Empresarials S.L.</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Aba Serveis Empresarials S.L.</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/sant-boi-de-llobregat/aba-serveis-empresarials-s-l-_008982217_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>equip de Asesoria Coope S.L.</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Asesoria Coope S.L.</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>https://www.asesoriacoope.es/es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>equip de I.M.S. Assessors Economics i Juridics S.L.</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>I.M.S. Assessors Economics i Juridics S.L.</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/a/asesoria-de-empresas/barcelona/sant-boi-de-llobregat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>equip de ASEMRECA S.L.U.</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>ASEMRECA S.L.U.</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/sant-boi-de-llobregat/asemreca-s-l-u-_196028658_000000002.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>equip de Arias Assessors (Sant Boi)</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Arias Assessors (Sant Boi)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>https://www.carakter.org/arias-assessors</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>equip de La Asesoría Sant Boi</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>La Asesoría Sant Boi</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Sant Boi de Llobregat</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>https://laasesoriasantboi.com/contacto/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>equip de Piera Asesorías y Servicios S.L.</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Piera Asesorías y Servicios S.L.</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>https://www.asesoriapiera.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>equip de Oficina de Gestión Centro S.L.P.</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Oficina de Gestión Centro S.L.P.</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>https://www.qdq.com/oficina-de-gestion-centro-514265</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>equip de Tapia Gestoría Administrativa</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Tapia Gestoría Administrativa</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>https://www.infoasesorias.es/tapia-gestoria-administrativa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>equip de K2 Assessors</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>K2 Assessors</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>https://directorio.guia33.com/item/k2-assessors-el-prat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>equip de MCC·GISE Asesoría</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>MCC·GISE Asesoría</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>https://asesoriamcc.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>equip de Asesoria Gestoria Integral de Pymes S.L.</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Asesoria Gestoria Integral de Pymes S.L.</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>https://www.cylex.es/el-prat-de-llobregat/asesoria-gestoria-integral-de-pymes-s-l--12503696.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>equip de Gestoria de la Cámara-Jonama S.L.</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Gestoria de la Cámara-Jonama S.L.</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/el-prat-de-llobregat/gestoria-de-la-camara-jonama-3764</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>equip de Fernández Rangel S.L.</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Fernández Rangel S.L.</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/el-prat-de-llobregat</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>equip de P&amp;G Consultores</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>P&amp;G Consultores</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>http://www.pygconsultores.net/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>equip de Asesoria Ricart S.L.</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Asesoria Ricart S.L.</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>https://empresite.eleconomista.es/ASESORIA-RICART.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>equip de Asesoria Teerre S.L.</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Asesoria Teerre S.L.</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>https://www.einforma.com/informacion-empresa/asesoria-teerre</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>equip de Plaça Pau Casals S.C.P.</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Plaça Pau Casals S.C.P.</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>El Prat de Llobregat</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/el-prat-de-llobregat/placa-pau-casals-s-c-p-_200511459_000000002.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>equip de Servicio Asesor Garantizado S.L.</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Servicio Asesor Garantizado S.L.</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/viladecans/servicio-asesor-garantizado-s-l-_204687479_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>equip de DRI Assessoria</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>DRI Assessoria</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>https://driassessoria.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>equip de Asesoría Laboral Geslab S.L.</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Asesoría Laboral Geslab S.L.</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/viladecans/asesoria-laboral-geslab-s-l-_021206677_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>equip de Baugar Gestora de Servicios</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Baugar Gestora de Servicios</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>https://es.kompass.com/c/baugar-gestora-de-servicios/es1284495/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>equip de Asesoría Areny</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Asesoría Areny</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/viladecans/asesoria-areny_008694648_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>equip de Fer Gestions 2009</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Fer Gestions 2009</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>https://empresite.eleconomista.es/FER-GESTIONS-2009.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>equip de Millán Gestió</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Millán Gestió</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>https://www.infoasesorias.es/millan-gestio/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>equip de Gómez i Carvacho Assessors</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Gómez i Carvacho Assessors</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>https://gomezcarvacho.com/nosotros/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>equip de JJ &amp; Assessors</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>JJ &amp; Assessors</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>https://assessoriajj.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>equip de Arias Assessors (Viladecans)</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Arias Assessors (Viladecans)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>https://www.carakter.org/arias-assessors</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>equip de Asesoría Empresarial Landa</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Asesoría Empresarial Landa</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>https://aelanda.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>equip de Gestram Associats 99</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Gestram Associats 99</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/viladecans/gestram-associats-99-6966</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>equip de Sm Gestió</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Sm Gestió</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/viladecans/sm-gestio-7263</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>equip de Paola Baquerizo Paladines</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Paola Baquerizo Paladines</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/viladecans/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>equip de Rafael C. Gil</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Rafael C. Gil</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/viladecans/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>equip de GIS, Grup Ip S.L.</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>GIS, Grup Ip S.L.</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Viladecans</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/barcelona/viladecans/gis-grup-ip-16315</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>equip de Fàbrega Consultors</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Fàbrega Consultors</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>https://www.fabregaconsultors.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>equip de Joan Tresserra Assessors S.L.</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Joan Tresserra Assessors S.L.</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>https://www.tresserra.cat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>equip de Bonafonte López S.C.P.</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Bonafonte López S.C.P.</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/molins-de-rei/bonafonte-lopez-s-c-p-_180378630_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>equip de Solgemp Asesores</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Solgemp Asesores</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>https://www.solgemp.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>equip de Ferransa Asesores</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Ferransa Asesores</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>https://ferransa.com/asesoria-fiscal-espana-molins-de-rei/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>equip de Vernet Assessors i Associats S.L.</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Vernet Assessors i Associats S.L.</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>https://www.paginasamarillas.es/f/molins-de-rei/vernet-assessors-i-associats-s-l-_021411855_000000001.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>equip de Servei d'Assessorament Empresarial i Consultors S.L.</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Servei d'Assessorament Empresarial i Consultors S.L.</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>https://www.einforma.com/informacion-empresa/servei-assessorament-empresarial-consultors</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>equip de NINOAFIC S.A.</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>NINOAFIC S.A.</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>sin email</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>https://www.citiservi.es/barcelona/ninoafic-molins-de-rei__926211_940.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>equip de Grup Gestor Molins de Rei</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Grup Gestor Molins de Rei</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Molins de Rei</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>aleix@centredegestions.com</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>https://www.cylex.es/molins-de-rei/grup-gestor-molins-de-rei-12661757.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>equip de Gestoria Font</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Gestoria Font</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>info@soldeges.com</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>https://fontgestoria.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>equip de Campdepadros Gestoria</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Campdepadros Gestoria</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>gestoria@campdepadros.cat</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>http://www.campdepadros.cat/contacte.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>equip de Corporació Raif S.L.</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Corporació Raif S.L.</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>info@habirent2005.com</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>https://www.gestorias.es/tarragona/43004</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>equip de Asde Assessors 2002</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Asde Assessors 2002</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>asde@asdeonline.com</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>https://www.asdeonline.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>equip de Vives i Roig S.L.</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Vives i Roig S.L.</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>catalan</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>info@vivesiroig.cat</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>https://www.empresia.es/empresa/vives-i-roig/</t>
         </is>
       </c>
     </row>
